--- a/nebullaone/docs/Vendor-Contractor-Workflow-Tracker.xlsx
+++ b/nebullaone/docs/Vendor-Contractor-Workflow-Tracker.xlsx
@@ -46,7 +46,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +78,11 @@
         <fgColor rgb="00F2F4F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FADF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,6 +132,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -312,6 +320,32 @@
     <tableColumn id="3" name="Files"/>
     <tableColumn id="4" name="Test IDs"/>
     <tableColumn id="5" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TestCases" displayName="TestCases" ref="A1:C82" headerRowCount="1">
+  <autoFilter ref="A1:C82"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Suite"/>
+    <tableColumn id="2" name="Test ID"/>
+    <tableColumn id="3" name="Scenario"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TestResults" displayName="TestResults" ref="A1:E82" headerRowCount="1">
+  <autoFilter ref="A1:E82"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Suite"/>
+    <tableColumn id="2" name="Test ID"/>
+    <tableColumn id="3" name="Scenario"/>
+    <tableColumn id="4" name="Actual result"/>
+    <tableColumn id="5" name="Result"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -670,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -689,7 +723,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -708,7 +742,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
@@ -727,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -746,7 +780,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -765,7 +799,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -784,7 +818,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -803,7 +837,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -822,7 +856,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -841,7 +875,7 @@
         <v>21</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -860,7 +894,7 @@
         <v>34</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -879,7 +913,7 @@
         <v>47</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
@@ -912,12 +946,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0/0 lifecycle steps in one clean run, registration → payment → performance → suspension → closure</t>
+          <t>14/14 lifecycle steps in one clean run, registration → payment → performance → suspension → closure</t>
         </is>
       </c>
     </row>
@@ -929,12 +963,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0/0 lifecycle steps, registration → contract → WBS/BOQ → work → measurement → billing → payment → handover → final bill → retention → closure</t>
+          <t>18/18 lifecycle steps, registration → contract → WBS/BOQ → work → measurement → billing → payment → handover → final bill → retention → closure</t>
         </is>
       </c>
     </row>
@@ -964,10 +998,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -977,10 +1011,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -990,10 +1024,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
@@ -1003,10 +1037,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -1016,10 +1050,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
@@ -1075,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1112,8 +1146,2198 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>G-27</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Submit registration with no documents</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>not created; form says "Upload before submitting…"</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>G-27b</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Save as draft still allowed without documents; submit from drawer blocked</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>draft VEN-014; after submit click status Draft; toast "Upload the required documents first — PAN Card not uploaded; GST Certi"</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>G-13a</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Wrong role cannot decide a vendor stage</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>as Priya (Proc. Exec.) Legal stage stays Pending; note shown: true</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>G-13b</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Legal Counsel approves; the same person cannot approve Finance</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Legal Approved by Neha Kulkarni; Finance stage shows block note: true</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Final approval blocked by open checklist (no WC insurance)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Approve disabled=true; checklist: Open before final approval: Workmen Compensation insurance: no policy on file</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>G-01b</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Finance Controller approves with override + reason (logged)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>status Active; override recorded: ["Workmen Compensation insurance: no policy on file"]</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Registration tier cannot be switched directly; request → Finance approval</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>tier dropdown present=false; request Pending; after requester tries to approve: Prospective; after Finance: Spend Authorized</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>G-28</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Hold past its release date ends automatically</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>VEN-006 status Active; audit: Hold ended on its release date — vendor back to Active</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>G-19</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate vendor bill number blocked</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>bill no. DST/26-27/0412 again → save disabled=true; message true</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>G-14</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Non-compliant vendor stopped at PO</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Stop note shown for Pioneer (GST certificate rejected)</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>G-05</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>On-hold (All) contractor: portal read-only</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>banner true; claim buttons 0</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>G-26</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Inactive vendor loses an open portal session</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Access suspended page shown</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>G-13c</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Payment needs Accounts/Finance role</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Stop: needs Accounts / Finance role</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>G-25a</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Retention release: requester and wrong role cannot approve</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>status Pending Approval; requester: "Retention-release approval needs the Finance Controller role"; Priya: "Retention-release approval needs the Finance Controller role"</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>G-25b</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Finance approves, approver cannot release, Accounts releases</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>after Rohit approve+release: Approved; after Anita: Released (approved by Rohit Shah, released by Anita Joshi)</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>G-13d</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>RA bill: each certification step needs its role and a different person</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Sneha sees "needs QS role"; Karan certified then approve → Certified ("Pm approval needs the Project Manager role — you a"); Vikram → Approved, payable INV-010</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>G-03a</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Contract for an unapproved contractor cannot be submitted</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Sign button absent; after submit: Draft; "Can't submit — Contractor is Pending Approval; Contractor is not spend"</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>G-03b</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>New contract: draft → Legal → Finance → sign (needs performance BG)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>CTR-007: submit → Pending Approval; after Legal+Finance → Approved; sign without BG: "Can't sign — Performance bank guarantee of ₹1.25 L (5%) not "; after BG → Active</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>G-22</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>BG register: extend and return</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>BG BG/AXIS/2026/0421 expiry now 2027-06-07; history 1</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Blocked contractor: contract hidden from WO picker; draft WO cannot be issued</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>picker has CTR-004: false; issue → Draft ("Can't issue — Contractor is Blacklisted; Contractor is block")</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>G-24</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>First work order waits for the mobilisation checklist</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Issue blocked: mobilisation checklist incomplete</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>G-21</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Suspend and resume a work order</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>suspend → Suspended (measure button 0); resume → In Progress</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>G-07</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Change order with a quantity line raises the WO quantity on approval</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>raiser approve: "Change-order approval needs the Project Manager ro"; after PM: WO-004 C1 qty 18500 (CO qty 500)</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>G-11</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Contract closure checklist blocks closing an active contract</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Close disabled=true; checklist shows yes</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>G-08/G-20</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Contractor RFQ award → draft contract with BOQ; recommendation required</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>button disabled without note=true; contract CTR-008 Draft for VEN-001, BOQ 2 lines, value 1300000 (non-compliant Sai excluded by the compliance gate)</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>G-23</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Contractor agrees a measurement in the portal; engineer countersigns without a paper sheet</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>agreed by Ramesh Patil; paper checkbox asked=false; JMS Signed, inspection Pending</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>G-12a</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Signed but uninspected measurement is not billable</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>WO-001 not offered — MB-016 waits for inspection</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>G-12b</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Inspection fails → NCR → QS certification of WO-001 blocked</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>NCR-003 Open; RA-003 note: Open NCR on WO-001 (NCR-003) — close it before certifying</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>G-12c</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Rework → re-inspection pass closes the NCR and makes the entry billable</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>after portal rework: Rework Done; after re-inspection: Closed; MB-016 inspection Passed</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>G-06</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Quantity above the WO blocks the RA bill until a change order raises it</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>before CO: submit disabled=true (over-quantity note); after CO-009 approved: disabled=false</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>G-16</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Unrecovered free-issue material is deducted automatically and linked to the bill</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>note: true; MI-002 recovered in RA-009; bill material deduction 36800</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>G-16b</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Rejecting that bill puts the material back for the next bill</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Sneha blocked on own bill: true; after reject MI-002 recoveredIn=null</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>G-15</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Equipment register and deployment on a work order</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>VEN-001 register rows 3; WO-001 deployments 3</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>G-15b</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Equipment with expired fitness cannot be deployed</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>"Tipper 10 cum: fitness / insurance expired 25 Sept 2026 — can't deploy"; deployed=false</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>G-17</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Daily progress report: add, duplicate date blocked</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>WO-002 reports 1; second report same day blocked=true</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>G-09</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Cost by WBS: budget → committed → executed → billed</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>WBS rows with budget/committed/executed shown</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>G-09b</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Work order needs a WBS element</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>save disabled without WBS=true, with WBS=false</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>G-18a</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Vendor submits an invoice in the portal → waits for AP review, not payable</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>INV-010 review=Pending; drawer shows AP review=true; payment button hidden</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>G-18b</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate invoice number rejected in the portal</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>duplicate blocked</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>G-18c</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>AP review: Procurement cannot accept; Accounts accepts → payable</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>as Priya: Pending; as Anita: Accepted (by Anita Joshi); payment button shown</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>G-18d</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Rejected invoice returns to the vendor; corrected invoice can be resubmitted</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>portal row shows Rejected=true; same number allowed again=true</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>G-10a</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Retention after DLP needs a handover certificate</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>raise disabled=true; "No handover certificate yet — issue it in Close-out &amp; Handover first"</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>G-10b</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Punch item blocks the final inspection until closed</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>inspection disabled with open snag=true; after contractor rectified + verified: disabled=false</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>G-10c</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Failed final inspection → snags to punch list; pass → handover certificate</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>snags after failed inspection 1; handover 2026-09-30 by Vikram Rao; status Active</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>G-10d</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Final bill settles remaining work and stops further billing</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>final checkbox preset=true; final bill RA-009 Submitted; WO-004 offered again=false</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>G-10e</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Stage tracker on the close-out list</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>CTR-004 row: Final payment</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>G-11b</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Fully settled contract (CTR-005) closes after retention release</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>open items before close: none; CTR-005 Closed, WO-006 Closed</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>G-11c</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Closed contract: measurement book frozen</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>WO-006 in measurement picker: false</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Registration (Tier 1) with documents — submitted</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>VEN-014 Pending Approval, 5 docs pending verification</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Final approval blocked until documents verified and qualification done</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Open before final approval: PAN Card: awaiting verification · GST Certificate: awaiting verification · Cancell</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Document verification + qualification</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>verified 5/5; qualification 91/100</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Approval Procurement → Legal → Finance (three people) → Active master</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Active / Spend Authorized; approvers Arjun Mehta, Neha Kulkarni, Rohit Shah</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>RFQ created and sent (new vendor + Konkan)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>RFQ-004 Sent, invited VEN-014, VEN-011</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Vendor quotes through the secure link</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>quote SST/Q/101 Under review</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Evaluation + award with recommendation → draft PO</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>PO-004 Draft for VEN-014, award note "Only compliant quote, L1"</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>PO approval by Procurement Head (not the buyer) → Issued</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>buyer tried: Draft; Arjun: Issued (approved by Arjun Mehta)</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>V09</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Delivery → goods receipt (acceptance)</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>1 GRN, received 40</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Vendor submits invoice in the portal → AP validation (Accounts) → accepted</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>INV-010 review Accepted by Anita Joshi; 3-way match against PO-004</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Payment (Finance — not the AP reviewer) → Paid</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>reviewer blocked: true; status paid by Rohit Shah</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>V12</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Performance: vendor gets a score after delivery</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>listed on the scorecard</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>V13</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Suspension: hold (All) makes the portal read-only; release restores</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>portal read-only while on hold</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Closure: vendor made inactive — portal access ends</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Inactive; portal: suspended</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Contractor registration with statutory documents</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>VEN-015 Pending Approval (Labor), 9 documents</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Technical / financial / legal / HSE qualification + insurance + document verification</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>docs verified 9/9; WC policy Verified; score 79</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Approval → contractor master Active</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Active / Spend Authorized</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Mobilisation checklist completed</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>7/7 done</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Tender (RFQ) with BOQ → contractor rate submission</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>RFQ-005: rate 178 submitted</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Technical + commercial evaluation → award as contract (BOQ carried over)</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>CTR-007 Draft, BOQ 3000 nos @ 178</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Contract approval Legal → Finance, performance BG, signing</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Active; approvals Legal Counsel: Neha Kulkarni, Finance Controller: Rohit Shah; signed by Arjun Mehta</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Project → WBS → work order from contract BOQ → contractor acceptance</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>WO-007 under Skyline Towers — Phase 1 › 1.1 Site enabling; line boqRef S1; acceptance Accepted</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Mobilisation on site: equipment, material issue, daily progress</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>equipment 1, material issues 1, DPRs 1</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Work execution → measurement → contractor agreement → JMS → inspection</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>MB-034: 1800 cum, JMS Signed (contractor agreed true), inspection Passed</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>RA bill (with material recovery) → verification → certification → approval → invoice → payment</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>RA-009: gross 320400, material 46000, retention 16020, net 274400; Submitted:Sneha Iyer → Verified:demo → Certified:Karan Desai → Approved:Vikram Rao → Paid:Anita Joshi; invoice INV-011</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Variation: extra quantity via change order (Project Manager approval)</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>WO qty now 3400 (CO +400)</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Balance work measured → WO completed</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>MB-035 1600 cum; WO Completed</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Performance rating</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>1 rating(s)</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Punch list → final inspection → handover certificate</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>handover 2026-09-30 by Vikram Rao; status Active (DLP running)</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Final bill → certification → final payment</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>RA-010 final=true Paid, gross 284800</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>DLP end → retention release (Finance approval, Accounts release) → BG returned</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>RR-002 ₹30260 Released (approved Rohit Shah, released Anita Joshi); BG Returned</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Contract closure — checklist complete, WO frozen</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>open before close: none; contract Closed, WO Closed</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Data continuity — one ID chain from registration to payment</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>vendor VEN-014 → RFQ-004 → PO-004 → INV-010 → paid | contractor VEN-015 → RFQ-005 → CTR-007 → Skyline Towers — Phase 1 › 1.1 Site enabling → BOQ S1 → WO-007 → RA-010, RA-009 → INV-012, INV-011 → paid → Closed</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -6858,7 +9082,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -6868,7 +9092,7 @@
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6910,7 +9134,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -6920,7 +9144,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -6962,7 +9186,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -6972,7 +9196,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7014,7 +9238,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -7024,7 +9248,7 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7066,7 +9290,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -7076,7 +9300,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7118,7 +9342,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -7128,7 +9352,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7170,7 +9394,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -7180,7 +9404,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7222,7 +9446,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -7232,7 +9456,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7274,7 +9498,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -7284,7 +9508,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7326,7 +9550,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -7336,7 +9560,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7378,7 +9602,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -7388,7 +9612,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7430,7 +9654,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -7440,7 +9664,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7482,7 +9706,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -7492,7 +9716,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7534,7 +9758,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -7544,7 +9768,7 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7586,7 +9810,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -7596,7 +9820,7 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7638,7 +9862,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -7648,7 +9872,7 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7690,7 +9914,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -7700,7 +9924,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7742,7 +9966,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -7752,7 +9976,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7794,7 +10018,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -7804,7 +10028,7 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7846,7 +10070,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -7856,7 +10080,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7898,7 +10122,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -7908,7 +10132,7 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -7950,7 +10174,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -7960,7 +10184,7 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8002,7 +10226,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -8012,7 +10236,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8054,7 +10278,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -8064,7 +10288,7 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8106,7 +10330,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -8116,7 +10340,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8158,7 +10382,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -8168,7 +10392,7 @@
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8210,7 +10434,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -8220,7 +10444,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8262,7 +10486,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -8272,7 +10496,7 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8314,7 +10538,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -8324,7 +10548,7 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8418,7 +10642,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
@@ -8428,7 +10652,7 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8522,7 +10746,7 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
@@ -8532,7 +10756,7 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8574,7 +10798,7 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -8584,7 +10808,7 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8626,7 +10850,7 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -8636,7 +10860,7 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8730,7 +10954,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -8740,7 +10964,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8782,7 +11006,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -8792,7 +11016,7 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8834,7 +11058,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -8844,7 +11068,7 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8886,7 +11110,7 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -8896,7 +11120,7 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -8990,7 +11214,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -9000,7 +11224,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9042,7 +11266,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -9052,7 +11276,7 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9094,7 +11318,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -9104,7 +11328,7 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9198,7 +11422,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -9208,7 +11432,7 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9250,7 +11474,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -9260,7 +11484,7 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9338,7 +11562,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9365,7 +11589,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9392,7 +11616,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9419,7 +11643,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9446,7 +11670,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9473,7 +11697,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9500,7 +11724,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9527,7 +11751,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9554,7 +11778,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9581,7 +11805,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9608,7 +11832,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9635,7 +11859,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9662,7 +11886,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9689,7 +11913,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9716,7 +11940,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9743,7 +11967,7 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9770,7 +11994,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9797,7 +12021,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9824,7 +12048,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9851,7 +12075,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9878,7 +12102,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9905,7 +12129,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9932,7 +12156,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9959,7 +12183,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -9986,7 +12210,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10013,7 +12237,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10040,7 +12264,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10067,7 +12291,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10094,7 +12318,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10148,7 +12372,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10202,7 +12426,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10229,7 +12453,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10256,7 +12480,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10310,7 +12534,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10337,7 +12561,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10364,7 +12588,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10391,7 +12615,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10445,7 +12669,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10472,7 +12696,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10499,7 +12723,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10553,7 +12777,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10580,7 +12804,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Fixed</t>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -10598,7 +12822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10623,7 +12847,1387 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>G-27</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Submit registration with no documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>G-27b</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Save as draft still allowed without documents; submit from drawer blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>G-13a</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Wrong role cannot decide a vendor stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>G-13b</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Legal Counsel approves; the same person cannot approve Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Final approval blocked by open checklist (no WC insurance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>G-01b</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Finance Controller approves with override + reason (logged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Registration tier cannot be switched directly; request → Finance approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>G-28</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Hold past its release date ends automatically</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>G-19</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate vendor bill number blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>G-14</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Non-compliant vendor stopped at PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>G-05</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>On-hold (All) contractor: portal read-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>G-26</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Inactive vendor loses an open portal session</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates, roles, SoD</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>G-13c</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Payment needs Accounts/Finance role</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>G-25a</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Retention release: requester and wrong role cannot approve</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>G-25b</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Finance approves, approver cannot release, Accounts releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>G-13d</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>RA bill: each certification step needs its role and a different person</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>G-03a</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Contract for an unapproved contractor cannot be submitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>G-03b</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>New contract: draft → Legal → Finance → sign (needs performance BG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>G-22</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>BG register: extend and return</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Blocked contractor: contract hidden from WO picker; draft WO cannot be issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>G-24</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>First work order waits for the mobilisation checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>G-21</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Suspend and resume a work order</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>G-07</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Change order with a quantity line raises the WO quantity on approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>G-11</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Contract closure checklist blocks closing an active contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>G-08/G-20</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Contractor RFQ award → draft contract with BOQ; recommendation required</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>G-23</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Contractor agrees a measurement in the portal; engineer countersigns without a paper sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>G-12a</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Signed but uninspected measurement is not billable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>G-12b</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Inspection fails → NCR → QS certification of WO-001 blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>G-12c</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Rework → re-inspection pass closes the NCR and makes the entry billable</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>G-06</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Quantity above the WO blocks the RA bill until a change order raises it</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>G-16</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Unrecovered free-issue material is deducted automatically and linked to the bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>G-16b</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Rejecting that bill puts the material back for the next bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>G-15</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Equipment register and deployment on a work order</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>G-15b</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Equipment with expired fitness cannot be deployed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>G-17</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Daily progress report: add, duplicate date blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>G-09</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Cost by WBS: budget → committed → executed → billed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>G-09b</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Work order needs a WBS element</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>G-18a</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Vendor submits an invoice in the portal → waits for AP review, not payable</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>G-18b</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate invoice number rejected in the portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>G-18c</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>AP review: Procurement cannot accept; Accounts accepts → payable</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>G-18d</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Rejected invoice returns to the vendor; corrected invoice can be resubmitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>G-10a</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Retention after DLP needs a handover certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>G-10b</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Punch item blocks the final inspection until closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>G-10c</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Failed final inspection → snags to punch list; pass → handover certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>G-10d</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Final bill settles remaining work and stops further billing</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>G-10e</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Stage tracker on the close-out list</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>G-11b</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Fully settled contract (CTR-005) closes after retention release</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>G-11c</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Closed contract: measurement book frozen</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Registration (Tier 1) with documents — submitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Final approval blocked until documents verified and qualification done</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Document verification + qualification</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Approval Procurement → Legal → Finance (three people) → Active master</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>RFQ created and sent (new vendor + Konkan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Vendor quotes through the secure link</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Evaluation + award with recommendation → draft PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>PO approval by Procurement Head (not the buyer) → Issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>V09</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Delivery → goods receipt (acceptance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Vendor submits invoice in the portal → AP validation (Accounts) → accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Payment (Finance — not the AP reviewer) → Paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>V12</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Performance: vendor gets a score after delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>V13</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Suspension: hold (All) makes the portal read-only; release restores</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Closure: vendor made inactive — portal access ends</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Contractor registration with statutory documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Technical / financial / legal / HSE qualification + insurance + document verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Approval → contractor master Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Mobilisation checklist completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Tender (RFQ) with BOQ → contractor rate submission</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Technical + commercial evaluation → award as contract (BOQ carried over)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Contract approval Legal → Finance, performance BG, signing</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Project → WBS → work order from contract BOQ → contractor acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Mobilisation on site: equipment, material issue, daily progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Work execution → measurement → contractor agreement → JMS → inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>RA bill (with material recovery) → verification → certification → approval → invoice → payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Variation: extra quantity via change order (Project Manager approval)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Balance work measured → WO completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Performance rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Punch list → final inspection → handover certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Final bill → certification → final payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>DLP end → retention release (Finance approval, Accounts release) → BG returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Contract closure — checklist complete, WO frozen</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Data continuity — one ID chain from registration to payment</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/nebullaone/docs/Vendor-Contractor-Workflow-Tracker.xlsx
+++ b/nebullaone/docs/Vendor-Contractor-Workflow-Tracker.xlsx
@@ -15,8 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status Model" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Tracker" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fix Tracker" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Merge Tracker" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Re-audit" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Results" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -224,7 +226,33 @@
     <tableColumn id="5" name="Entry"/>
     <tableColumn id="6" name="Key actions"/>
     <tableColumn id="7" name="Next"/>
-    <tableColumn id="8" name="Roles"/>
+    <tableColumn id="8" name="Owner (department)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="TestCases" displayName="TestCases" ref="A1:C101" headerRowCount="1">
+  <autoFilter ref="A1:C101"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Suite"/>
+    <tableColumn id="2" name="Test ID"/>
+    <tableColumn id="3" name="Scenario"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TestResults" displayName="TestResults" ref="A1:E101" headerRowCount="1">
+  <autoFilter ref="A1:E101"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Suite"/>
+    <tableColumn id="2" name="Test ID"/>
+    <tableColumn id="3" name="Scenario"/>
+    <tableColumn id="4" name="Actual result"/>
+    <tableColumn id="5" name="Result"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -252,7 +280,7 @@
     <tableColumn id="1" name="Step"/>
     <tableColumn id="2" name="Stage"/>
     <tableColumn id="3" name="Screen"/>
-    <tableColumn id="4" name="Role"/>
+    <tableColumn id="4" name="Owner (department)"/>
     <tableColumn id="5" name="Status in"/>
     <tableColumn id="6" name="Status out"/>
     <tableColumn id="7" name="Gate / validation"/>
@@ -268,7 +296,7 @@
     <tableColumn id="1" name="Step"/>
     <tableColumn id="2" name="Stage"/>
     <tableColumn id="3" name="Screen"/>
-    <tableColumn id="4" name="Role"/>
+    <tableColumn id="4" name="Owner (department)"/>
     <tableColumn id="5" name="Status in"/>
     <tableColumn id="6" name="Status out"/>
     <tableColumn id="7" name="Gate / validation"/>
@@ -285,7 +313,7 @@
     <tableColumn id="2" name="From"/>
     <tableColumn id="3" name="Action"/>
     <tableColumn id="4" name="To"/>
-    <tableColumn id="5" name="Who"/>
+    <tableColumn id="5" name="Usually done by"/>
     <tableColumn id="6" name="Rule"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
@@ -326,26 +354,28 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TestCases" displayName="TestCases" ref="A1:C82" headerRowCount="1">
-  <autoFilter ref="A1:C82"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="Suite"/>
-    <tableColumn id="2" name="Test ID"/>
-    <tableColumn id="3" name="Scenario"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="MergeTracker" displayName="MergeTracker" ref="A1:F28" headerRowCount="1">
+  <autoFilter ref="A1:F28"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Area"/>
+    <tableColumn id="3" name="Requirement"/>
+    <tableColumn id="4" name="How it works now"/>
+    <tableColumn id="5" name="Test IDs"/>
+    <tableColumn id="6" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TestResults" displayName="TestResults" ref="A1:E82" headerRowCount="1">
-  <autoFilter ref="A1:E82"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Suite"/>
-    <tableColumn id="2" name="Test ID"/>
-    <tableColumn id="3" name="Scenario"/>
-    <tableColumn id="4" name="Actual result"/>
-    <tableColumn id="5" name="Result"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Reaudit" displayName="Reaudit" ref="A1:D11" headerRowCount="1">
+  <autoFilter ref="A1:D11"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Section"/>
+    <tableColumn id="2" name="Check"/>
+    <tableColumn id="3" name="Result"/>
+    <tableColumn id="4" name="Evidence"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -640,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -660,7 +690,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Source: NebullaOne-WFM.html (nebullaone/src). Every gap from the end-to-end audit (G-01…G-28) plus 19 issues found during the fix → retest loop (N-01…N-19).</t>
+          <t>Source: NebullaOne-WFM.html (nebullaone/src). Every gap from the end-to-end audit (G-01…G-28), 19 issues found during the fix loop (N-01…N-19), and 27 items merged from the second build (MG-01…MG-27), re-audited after roles were removed.</t>
         </is>
       </c>
     </row>
@@ -687,6 +717,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Withdrawn (roles removed)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Remaining</t>
         </is>
       </c>
@@ -709,6 +744,9 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -720,12 +758,15 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -747,6 +788,9 @@
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -766,6 +810,9 @@
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -785,6 +832,9 @@
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -796,12 +846,15 @@
         <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -823,6 +876,9 @@
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -842,6 +898,9 @@
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -861,6 +920,9 @@
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -872,12 +934,15 @@
         <v>21</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -891,12 +956,15 @@
         <v>34</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -910,191 +978,245 @@
         <v>47</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Merged items (MG-01…MG-27)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Workflow</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Vendor workflow</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>14/14 lifecycle steps in one clean run, registration → payment → performance → suspension → closure</t>
-        </is>
-      </c>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Vendor workflow</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>14/14 lifecycle steps in one clean run, registration → payment → performance → suspension → closure</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Contractor workflow</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>18/18 lifecycle steps, registration → contract → WBS/BOQ → work → measurement → billing → payment → handover → final bill → retention → closure</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Test runs</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>13</v>
-      </c>
-      <c r="C23" t="n">
-        <v>13</v>
-      </c>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Final full-system test</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B29" t="n">
         <v>33</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C29" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>• No Excel workbook was supplied with the request, so this workbook was created fresh (it has no 'original sheets').</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>• Roles are demo personas chosen from the 'Acting as' menu; the signed-in user is an administrator with every role but is still bound by segregation of duties.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>• Business rules not specified by the user follow common enterprise practice (Legal → Finance contract approval, 5% performance BG, retention released after DLP, qualification pass mark 70). All gates are configurable in Procurement Settings where noted.</t>
+          <t>• The benchmark is the tracker workbook from the previous round (docs/Vendor-Contractor-Workflow-Tracker.xlsx); this re-audit regenerates it with the merged items, the Re-audit sheet and the roles removal.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>• Retention release after the defect liability period was tested by moving the handover date back (time travel); everything else ran on real dates.</t>
+          <t>• Roles were removed at your request. The signed-in user can do every step. Approvals still go stage by stage, and each action is logged with the user and time.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>• Data lives in browser localStorage (no backend); e-mails and one-time codes are shown on screen.</t>
+          <t>• Rules not spelled out in the request follow common practice: qualification pass mark 70, default value limit ₹10 Cr (score ≥ 70) or ₹50 Cr (score ≥ 85), background check valid for 12 months, hold release within a year, CAP due within 180 days, 5% performance BG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>• 'Not assessed' and 'Not qualified' contractors can't be issued work orders. 'Expired' qualification follows the PO compliance gate in Procurement Settings. Going over the value limit is a warning, not a block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>• Merged items marked 'Built — no automated test' were built and compile, but no test suite exercises them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>• Retention release after the defect liability period was tested by moving the handover date back. Everything else ran on real dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>• The prototype has no backend: data lives in the browser (localStorage), and e-mails and one-time codes are shown on screen.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1231,2011 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>A. Overall workflow coverage</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Both lifecycles ran end to end through the UI from a clean start on the final build: vendor 14/14 steps, contractor 18/18 steps. 30 screens are mapped in the workbook and 27 items from the second build are merged.</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Final suite V01–V15 / C01–C18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>B. Critical broken mappings</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Every high-severity gap from the audit, re-checked on the final build. None is open.</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>11 audit gaps, 0 merged items</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>C. Missing modules / screens</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Steps and screens that did not exist at audit time, plus the screens added in the merge: Select payable, Accruals, the approval-stage editor, the background-check form, qualification outcome and the quote exchange rate.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>12 audit gaps, 6 merged items</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>D. Orphan modules / screens</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Screens that could not be reached, or led nowhere. Every menu page opens without errors (smoke run over all routes); deep links open the right record.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>1 audit gaps, 0 merged items</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>E. Data continuity issues</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>One ID chain runs from registration to payment for each flow. The chain below is from the final run.</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>7 audit gaps, 0 merged items</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>F. Approval issues</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Approvals run stage by stage with checklists and gates. At your request the role model was removed: there is no 'Acting as' switcher, no per-step role check and no one-person-per-step rule. The fixes that depended on it are marked Withdrawn. Approval stages are now configurable in Procurement Settings.</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>13 audit gaps, 2 merged items</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>G. Status issues</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Status transitions that were missing or unenforced. The full status model is in the workbook (Status Model sheet).</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>6 audit gaps, 0 merged items</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>H. Exception handling issues</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Validation and exception paths, including the form checks merged from the second build. Items marked 'Built — no automated test' are in the code and were not exercised by a test suite.</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>8 audit gaps, 19 merged items</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>I. Contractor-specific chain</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Registration → qualification (status and value limit) → background check → approval → mobilisation → tender → contract → WBS / BOQ → work order → measurement → RA bills → change orders → handover → final bill → retention → closure.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>30 audit gaps, 6 merged items</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>J. Corrected end-to-end workflow</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>The workflow as it now runs in the prototype. The owner column names the department that usually does the step; with roles removed, the app does not enforce it.</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Workflow Vendor / Workflow Contractor sheets</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Suite</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>No "Acting as" switcher on any page</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>M-01</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Bank account added from the Bank tab starts Unverified; Verify stamps who and when</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>M-02</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Bank form rejects a bad IFSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>M-03</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Upload limit: a file above 5 MB is refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate bill number blocked ignoring case and spaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Payment date in the future is refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Select payable and Accruals are available on Vendor Bills</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>P-01</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>RFQ: one vendor only is refused (≥ 2 vendors needed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Labour rate below the statutory minimum wage is refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Add worker: under-18 date of birth is refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Q-01</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Qualification results show status and value limit (incl. "Qualified with exceptions")</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Q-02</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Work order above the contractor's qualification limit shows a warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Q-03</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Background check not clear → work order cannot be issued (mobilisation blocked)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Q-04</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Recording an adverse background check needs a finding</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Hold: short reason and past release date are refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Insurance: an already-expired policy is refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Performance rating of 2 or below needs remarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Approval stages are configurable: a new Compliance stage is used by the next registration</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>S-02</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Existing records keep their stages; an empty stage name is refused</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>G-27</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Submit registration with no documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>G-27b</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Save as draft still allowed without documents; submit from drawer blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>G-13a</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Roles removed: no "Acting as" switcher; the pending stage can be decided by the signed-in user</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>G-13b</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Stages still run in order: Finance opens only after Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Final approval blocked by open checklist (no WC insurance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>G-01b</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Finance Controller approves with override + reason (logged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Registration tier cannot be switched directly; request → Finance approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>G-28</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Hold past its release date ends automatically</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>G-19</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate vendor bill number blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>G-14</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Non-compliant vendor stopped at PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>G-05</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>On-hold (All) contractor: portal read-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>G-26</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Inactive vendor loses an open portal session</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Batch 1 — vendor gates and approvals</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>G-13c</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Payment dialog has no role check (roles removed) but keeps the payment gates</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>G-25a</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Retention release: must be approved before it can be released</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>G-25b</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Approve, then release — status Approved → Released with both steps logged</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>G-13d</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>RA bill: certification steps run in order (Verified → Certified → Approved) and approval creates the payable</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>G-03a</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Contract for an unapproved contractor cannot be submitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>G-03b</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>New contract: draft → Legal → Finance → sign (needs performance BG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>G-22</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>BG register: extend and return</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Blocked contractor: contract hidden from WO picker; draft WO cannot be issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>G-24</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>First work order waits for the mobilisation checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>G-21</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Suspend and resume a work order</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>G-07</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Change order with a quantity line raises the WO quantity on approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>G-11</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Contract closure checklist blocks closing an active contract</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>G-08/G-20</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Contractor RFQ award → draft contract with BOQ; recommendation required</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>G-23</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Contractor agrees a measurement in the portal; engineer countersigns without a paper sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>G-12a</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Signed but uninspected measurement is not billable</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>G-12b</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Inspection fails → NCR → QS certification of WO-001 blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>G-12c</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Rework → re-inspection pass closes the NCR and makes the entry billable</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>G-06</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Quantity above the WO blocks the RA bill until a change order raises it</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>G-16</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Unrecovered free-issue material is deducted automatically and linked to the bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>G-16b</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Rejecting that bill puts the material back for the next bill</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>G-15</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Equipment register and deployment on a work order</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>G-15b</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Equipment with expired fitness cannot be deployed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>G-17</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Daily progress report: add, duplicate date blocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>G-09</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Cost by WBS: budget → committed → executed → billed</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Batch 4 — quantity &amp; execution</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>G-09b</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Work order needs a WBS element</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>G-18a</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Vendor submits an invoice in the portal → waits for AP review, not payable</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>G-18b</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate invoice number rejected in the portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>G-18c</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>AP review: invoice can't be paid until accepted; accepting makes it payable</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>G-18d</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Rejected invoice returns to the vendor; corrected invoice can be resubmitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>G-10a</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Retention after DLP needs a handover certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>G-10b</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Punch item blocks the final inspection until closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>G-10c</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Failed final inspection → snags to punch list; pass → handover certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>G-10d</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Final bill settles remaining work and stops further billing</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>G-10e</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Stage tracker on the close-out list</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>G-11b</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Fully settled contract (CTR-005) closes after retention release</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>G-11c</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Closed contract: measurement book frozen</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>V01</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Registration (Tier 1) with documents — submitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>V02</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Final approval blocked until documents verified and qualification done</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>V03</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Document verification + qualification</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>V04</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Approval Procurement → Legal → Finance (all three stages) → Active master</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>V05</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>RFQ created and sent (new vendor + Konkan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>V06</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Vendor quotes through the secure link</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>V07</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Evaluation + award with recommendation → draft PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>V08</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>PO approval (Approval Management) → Issued</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>V09</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Delivery → goods receipt (acceptance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>V10</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Vendor submits invoice in the portal → AP validation (Accounts) → accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Payment (after AP acceptance) → Paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>V12</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Performance: vendor gets a score after delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>V13</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Suspension: hold (All) makes the portal read-only; release restores</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Closure: vendor made inactive — portal access ends</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Contractor registration with statutory documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Technical / financial / legal / HSE qualification + insurance + document verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Approval → contractor master Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Mobilisation: blocked until the background check is clear, then checklist completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Tender (RFQ) with BOQ → contractor rate submission</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Technical + commercial evaluation → award as contract (BOQ carried over)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Contract approval Legal → Finance, performance BG, signing</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Project → WBS → work order from contract BOQ → contractor acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Mobilisation on site: equipment, material issue, daily progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Work execution → measurement → contractor agreement → JMS → inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>RA bill (with material recovery) → verification → certification → approval → invoice → payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Variation: extra quantity via change order (Project Manager approval)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Balance work measured → WO completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Performance rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Punch list → final inspection → handover certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Final bill → certification → final payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>DLP end → retention release (Finance approval, Accounts release) → BG returned</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Contract closure — checklist complete, WO frozen</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Data continuity — one ID chain from registration to payment</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1149,22 +3275,22 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>G-27</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Submit registration with no documents</t>
+          <t>No "Acting as" switcher on any page</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>not created; form says "Upload before submitting…"</t>
+          <t>pages showing the switcher: 0</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
@@ -1176,22 +3302,22 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>G-27b</t>
+          <t>M-01</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Save as draft still allowed without documents; submit from drawer blocked</t>
+          <t>Bank account added from the Bank tab starts Unverified; Verify stamps who and when</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>draft VEN-014; after submit click status Draft; toast "Upload the required documents first — PAN Card not uploaded; GST Certi"</t>
+          <t>added Unverified; after verify Verified by demo</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
@@ -1203,22 +3329,22 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>G-13a</t>
+          <t>M-02</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Wrong role cannot decide a vendor stage</t>
+          <t>Bank form rejects a bad IFSC</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>as Priya (Proc. Exec.) Legal stage stays Pending; note shown: true</t>
+          <t>IFSC error shown: true; saved 0</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -1230,22 +3356,22 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>G-13b</t>
+          <t>M-03</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Legal Counsel approves; the same person cannot approve Finance</t>
+          <t>Upload limit: a file above 5 MB is refused</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Legal Approved by Neha Kulkarni; Finance stage shows block note: true</t>
+          <t>toast: "File is 5.00 MB — over the 5 MB limit"; docs unchanged: true</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -1257,22 +3383,22 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>B-01</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Final approval blocked by open checklist (no WC insurance)</t>
+          <t>Duplicate bill number blocked ignoring case and spaces</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Approve disabled=true; checklist: Open before final approval: Workmen Compensation insurance: no policy on file</t>
+          <t>"dst/26-27/0412" with spaces → save disabled=true</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -1284,22 +3410,22 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>G-01b</t>
+          <t>B-02</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Finance Controller approves with override + reason (logged)</t>
+          <t>Payment date in the future is refused</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>status Active; override recorded: ["Workmen Compensation insurance: no policy on file"]</t>
+          <t>value date 2026-10-05 → message true; release disabled=true</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1311,22 +3437,22 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>B-03</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Registration tier cannot be switched directly; request → Finance approval</t>
+          <t>Select payable and Accruals are available on Vendor Bills</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>tier dropdown present=false; request Pending; after requester tries to approve: Prospective; after Finance: Spend Authorized</t>
+          <t>select payable: true; accruals view: true</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1338,22 +3464,22 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>G-28</t>
+          <t>P-01</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Hold past its release date ends automatically</t>
+          <t>RFQ: one vendor only is refused (≥ 2 vendors needed)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>VEN-006 status Active; audit: Hold ended on its release date — vendor back to Active</t>
+          <t>message: at least two vendorsCancelSave &amp; compose e-mail; disabled=true</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1365,22 +3491,22 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>G-19</t>
+          <t>C-01</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Duplicate vendor bill number blocked</t>
+          <t>Labour rate below the statutory minimum wage is refused</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>bill no. DST/26-27/0412 again → save disabled=true; message true</t>
+          <t>message shown: true</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1392,22 +3518,22 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>G-14</t>
+          <t>C-02</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Non-compliant vendor stopped at PO</t>
+          <t>Add worker: under-18 date of birth is refused</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Stop note shown for Pioneer (GST certificate rejected)</t>
+          <t>DOB 2010-10-04 → 18+ message: true</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1419,22 +3545,22 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>G-05</t>
+          <t>Q-01</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>On-hold (All) contractor: portal read-only</t>
+          <t>Qualification results show status and value limit (incl. "Qualified with exceptions")</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>banner true; claim buttons 0</t>
+          <t>with exceptions: true; value limit column: true</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1446,22 +3572,22 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>G-26</t>
+          <t>Q-02</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Inactive vendor loses an open portal session</t>
+          <t>Work order above the contractor's qualification limit shows a warning</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Access suspended page shown</t>
+          <t>Over the qualification limit — open work ₹3</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -1473,22 +3599,22 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>G-13c</t>
+          <t>Q-03</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Payment needs Accounts/Finance role</t>
+          <t>Background check not clear → work order cannot be issued (mobilisation blocked)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Stop: needs Accounts / Finance role</t>
+          <t>note: true; issue disabled=true</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1500,22 +3626,22 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>G-25a</t>
+          <t>Q-04</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Retention release: requester and wrong role cannot approve</t>
+          <t>Recording an adverse background check needs a finding</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>status Pending Approval; requester: "Retention-release approval needs the Finance Controller role"; Priya: "Retention-release approval needs the Finance Controller role"</t>
+          <t>save disabled=true; message true</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -1527,22 +3653,22 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>G-25b</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Finance approves, approver cannot release, Accounts releases</t>
+          <t>Hold: short reason and past release date are refused</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>after Rohit approve+release: Approved; after Anita: Released (approved by Rohit Shah, released by Anita Joshi)</t>
+          <t>short reason disabled=true; past date disabled=true (true)</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1554,22 +3680,22 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>G-13d</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>RA bill: each certification step needs its role and a different person</t>
+          <t>Insurance: an already-expired policy is refused</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Sneha sees "needs QS role"; Karan certified then approve → Certified ("Pm approval needs the Project Manager role — you a"); Vikram → Approved, payable INV-010</t>
+          <t xml:space="preserve">save disabled=true; Policy has already expired </t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -1581,22 +3707,22 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>G-03a</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Contract for an unapproved contractor cannot be submitted</t>
+          <t>Performance rating of 2 or below needs remarks</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Sign button absent; after submit: Draft; "Can't submit — Contractor is Pending Approval; Contractor is not spend"</t>
+          <t>save disabled=true; remarks message true</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1608,22 +3734,22 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>G-03b</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>New contract: draft → Legal → Finance → sign (needs performance BG)</t>
+          <t>Approval stages are configurable: a new Compliance stage is used by the next registration</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>CTR-007: submit → Pending Approval; after Legal+Finance → Approved; sign without BG: "Can't sign — Performance bank guarantee of ₹1.25 L (5%) not "; after BG → Active</t>
+          <t>settings: Procurement → Legal → Finance → Compliance; new vendor stages: Procurement → Legal → Finance → Compliance</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -1635,22 +3761,22 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Merge — merged validations, qualification, background check, approval stages, roles removed</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>G-22</t>
+          <t>S-02</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>BG register: extend and return</t>
+          <t>Existing records keep their stages; an empty stage name is refused</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>BG BG/AXIS/2026/0421 expiry now 2027-06-07; history 1</t>
+          <t>VEN-007 stages 3; empty name → "Vendor approval: every stage needs a name"; saved flow Procurement → Legal → Finance → Compliance</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -1662,22 +3788,22 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-27</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Blocked contractor: contract hidden from WO picker; draft WO cannot be issued</t>
+          <t>Submit registration with no documents</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>picker has CTR-004: false; issue → Draft ("Can't issue — Contractor is Blacklisted; Contractor is block")</t>
+          <t>not created; form says "Upload before submitting…"</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1689,22 +3815,22 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>G-24</t>
+          <t>G-27b</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>First work order waits for the mobilisation checklist</t>
+          <t>Save as draft still allowed without documents; submit from drawer blocked</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Issue blocked: mobilisation checklist incomplete</t>
+          <t>draft VEN-014; after submit click status Draft; toast "Upload the required documents first — PAN Card not uploaded; GST Certi"</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -1716,22 +3842,22 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>G-21</t>
+          <t>G-13a</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Suspend and resume a work order</t>
+          <t>Roles removed: no "Acting as" switcher; the pending stage can be decided by the signed-in user</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>suspend → Suspended (measure button 0); resume → In Progress</t>
+          <t>switcher shown: false; Legal Approved by demo</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -1743,22 +3869,22 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>G-13b</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Change order with a quantity line raises the WO quantity on approval</t>
+          <t>Stages still run in order: Finance opens only after Legal</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>raiser approve: "Change-order approval needs the Project Manager ro"; after PM: WO-004 C1 qty 18500 (CO qty 500)</t>
+          <t>Procurement Approved → Legal Approved → Finance Pending</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -1770,22 +3896,22 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>G-11</t>
+          <t>G-01</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Contract closure checklist blocks closing an active contract</t>
+          <t>Final approval blocked by open checklist (no WC insurance)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Close disabled=true; checklist shows yes</t>
+          <t>Approve disabled=true; checklist: Open before final approval: Workmen Compensation insurance: no policy on file</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -1797,22 +3923,22 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>G-08/G-20</t>
+          <t>G-01b</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Contractor RFQ award → draft contract with BOQ; recommendation required</t>
+          <t>Finance Controller approves with override + reason (logged)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>button disabled without note=true; contract CTR-008 Draft for VEN-001, BOQ 2 lines, value 1300000 (non-compliant Sai excluded by the compliance gate)</t>
+          <t>status Active; override recorded: ["Workmen Compensation insurance: no policy on file"]</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -1824,22 +3950,22 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>G-23</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Contractor agrees a measurement in the portal; engineer countersigns without a paper sheet</t>
+          <t>Registration tier cannot be switched directly; request → Finance approval</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>agreed by Ramesh Patil; paper checkbox asked=false; JMS Signed, inspection Pending</t>
+          <t>tier dropdown present=false; request Pending (tier still Prospective); after approval: Spend Authorized</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -1851,22 +3977,22 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>G-12a</t>
+          <t>G-28</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Signed but uninspected measurement is not billable</t>
+          <t>Hold past its release date ends automatically</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>WO-001 not offered — MB-016 waits for inspection</t>
+          <t>VEN-006 status Active; audit: Hold ended on its release date — vendor back to Active</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -1878,22 +4004,22 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>G-12b</t>
+          <t>G-19</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Inspection fails → NCR → QS certification of WO-001 blocked</t>
+          <t>Duplicate vendor bill number blocked</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>NCR-003 Open; RA-003 note: Open NCR on WO-001 (NCR-003) — close it before certifying</t>
+          <t>bill no. DST/26-27/0412 again → save disabled=true; message true</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -1905,22 +4031,22 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>G-12c</t>
+          <t>G-14</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Rework → re-inspection pass closes the NCR and makes the entry billable</t>
+          <t>Non-compliant vendor stopped at PO</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>after portal rework: Rework Done; after re-inspection: Closed; MB-016 inspection Passed</t>
+          <t>Stop note shown for Pioneer (GST certificate rejected)</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
@@ -1932,22 +4058,22 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>G-06</t>
+          <t>G-05</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Quantity above the WO blocks the RA bill until a change order raises it</t>
+          <t>On-hold (All) contractor: portal read-only</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>before CO: submit disabled=true (over-quantity note); after CO-009 approved: disabled=false</t>
+          <t>banner true; claim buttons 0</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -1959,22 +4085,22 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>G-16</t>
+          <t>G-26</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Unrecovered free-issue material is deducted automatically and linked to the bill</t>
+          <t>Inactive vendor loses an open portal session</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>note: true; MI-002 recovered in RA-009; bill material deduction 36800</t>
+          <t>Access suspended page shown</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -1986,22 +4112,22 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batch 1 — vendor gates and approvals</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>G-16b</t>
+          <t>G-13c</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Rejecting that bill puts the material back for the next bill</t>
+          <t>Payment dialog has no role check (roles removed) but keeps the payment gates</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Sneha blocked on own bill: true; after reject MI-002 recoveredIn=null</t>
+          <t>role note: false; dialog: Record payment — INV-004TDS is withheld at payment for PO bills; RA bills alread</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -2013,22 +4139,22 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>G-15</t>
+          <t>G-25a</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Equipment register and deployment on a work order</t>
+          <t>Retention release: must be approved before it can be released</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>VEN-001 register rows 3; WO-001 deployments 3</t>
+          <t>status Pending Approval; release button before approval: 0</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -2040,22 +4166,22 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>G-15b</t>
+          <t>G-25b</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Equipment with expired fitness cannot be deployed</t>
+          <t>Approve, then release — status Approved → Released with both steps logged</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>"Tipper 10 cum: fitness / insurance expired 25 Sept 2026 — can't deploy"; deployed=false</t>
+          <t>after approve: Approved; after release: Released (approved by demo, released by demo)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -2067,22 +4193,22 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>G-17</t>
+          <t>G-13d</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Daily progress report: add, duplicate date blocked</t>
+          <t>RA bill: certification steps run in order (Verified → Certified → Approved) and approval creates the payable</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>WO-002 reports 1; second report same day blocked=true</t>
+          <t>Verified (approve offered: false) → Certified → Approved, payable INV-010</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -2094,22 +4220,22 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>G-09</t>
+          <t>G-03a</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Cost by WBS: budget → committed → executed → billed</t>
+          <t>Contract for an unapproved contractor cannot be submitted</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>WBS rows with budget/committed/executed shown</t>
+          <t>Sign button absent; after submit: Draft; "Can't submit — Contractor is Pending Approval; Contractor is not spend"</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -2121,22 +4247,22 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>G-09b</t>
+          <t>G-03b</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Work order needs a WBS element</t>
+          <t>New contract: draft → Legal → Finance → sign (needs performance BG)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>save disabled without WBS=true, with WBS=false</t>
+          <t>CTR-007: submit → Pending Approval; after Legal+Finance → Approved; sign without BG: "Can't sign — Performance bank guarantee of ₹1.25 L (5%) not "; after BG → Active</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -2148,22 +4274,22 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>G-18a</t>
+          <t>G-22</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Vendor submits an invoice in the portal → waits for AP review, not payable</t>
+          <t>BG register: extend and return</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>INV-010 review=Pending; drawer shows AP review=true; payment button hidden</t>
+          <t>BG BG/AXIS/2026/0421 expiry now 2027-06-07; history 1</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
@@ -2175,22 +4301,22 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>G-18b</t>
+          <t>G-04</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Duplicate invoice number rejected in the portal</t>
+          <t>Blocked contractor: contract hidden from WO picker; draft WO cannot be issued</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>duplicate blocked</t>
+          <t>picker has CTR-004: false; issue → Draft ("Can't issue — Contractor is Blacklisted; Contractor is block")</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
@@ -2202,22 +4328,22 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>G-18c</t>
+          <t>G-24</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>AP review: Procurement cannot accept; Accounts accepts → payable</t>
+          <t>First work order waits for the mobilisation checklist</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>as Priya: Pending; as Anita: Accepted (by Anita Joshi); payment button shown</t>
+          <t>Issue blocked: mobilisation checklist incomplete</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
@@ -2229,22 +4355,22 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>G-18d</t>
+          <t>G-21</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Rejected invoice returns to the vendor; corrected invoice can be resubmitted</t>
+          <t>Suspend and resume a work order</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>portal row shows Rejected=true; same number allowed again=true</t>
+          <t>suspend → Suspended (measure button 0); resume → In Progress</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
@@ -2256,22 +4382,22 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>G-10a</t>
+          <t>G-07</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Retention after DLP needs a handover certificate</t>
+          <t>Change order with a quantity line raises the WO quantity on approval</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>raise disabled=true; "No handover certificate yet — issue it in Close-out &amp; Handover first"</t>
+          <t>approve: "CO-001 approved"; after approval: WO-004 C1 qty 18500 (CO qty 500)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -2283,22 +4409,22 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>G-10b</t>
+          <t>G-11</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Punch item blocks the final inspection until closed</t>
+          <t>Contract closure checklist blocks closing an active contract</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>inspection disabled with open snag=true; after contractor rectified + verified: disabled=false</t>
+          <t>Close disabled=true; checklist shows yes</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
@@ -2310,22 +4436,22 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>G-10c</t>
+          <t>G-08/G-20</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Failed final inspection → snags to punch list; pass → handover certificate</t>
+          <t>Contractor RFQ award → draft contract with BOQ; recommendation required</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>snags after failed inspection 1; handover 2026-09-30 by Vikram Rao; status Active</t>
+          <t>button disabled without note=true; contract CTR-008 Draft for VEN-001, BOQ 2 lines, value 1300000 (non-compliant Sai excluded by the compliance gate)</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
@@ -2337,22 +4463,22 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>G-10d</t>
+          <t>G-23</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Final bill settles remaining work and stops further billing</t>
+          <t>Contractor agrees a measurement in the portal; engineer countersigns without a paper sheet</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>final checkbox preset=true; final bill RA-009 Submitted; WO-004 offered again=false</t>
+          <t>agreed by Ramesh Patil; paper checkbox asked=false; JMS Signed, inspection Pending</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -2364,22 +4490,22 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>G-10e</t>
+          <t>G-12a</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Stage tracker on the close-out list</t>
+          <t>Signed but uninspected measurement is not billable</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>CTR-004 row: Final payment</t>
+          <t>WO-001 not offered — MB-016 waits for inspection</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
@@ -2391,22 +4517,22 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>G-11b</t>
+          <t>G-12b</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Fully settled contract (CTR-005) closes after retention release</t>
+          <t>Inspection fails → NCR → QS certification of WO-001 blocked</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>open items before close: none; CTR-005 Closed, WO-006 Closed</t>
+          <t>NCR-003 Open; RA-003 note: Open NCR on WO-001 (NCR-003) — close it before certifying</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
@@ -2418,22 +4544,22 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>G-11c</t>
+          <t>G-12c</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Closed contract: measurement book frozen</t>
+          <t>Rework → re-inspection pass closes the NCR and makes the entry billable</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>WO-006 in measurement picker: false</t>
+          <t>after portal rework: Rework Done; after re-inspection: Closed; MB-016 inspection Passed</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
@@ -2445,22 +4571,22 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>V01</t>
+          <t>G-06</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Registration (Tier 1) with documents — submitted</t>
+          <t>Quantity above the WO blocks the RA bill until a change order raises it</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>VEN-014 Pending Approval, 5 docs pending verification</t>
+          <t>before CO: submit disabled=true (over-quantity note); after CO-009 approved: disabled=false</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
@@ -2472,22 +4598,22 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>V02</t>
+          <t>G-16</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Final approval blocked until documents verified and qualification done</t>
+          <t>Unrecovered free-issue material is deducted automatically and linked to the bill</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Open before final approval: PAN Card: awaiting verification · GST Certificate: awaiting verification · Cancell</t>
+          <t>note: true; MI-002 recovered in RA-009; bill material deduction 36800</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -2499,22 +4625,22 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>V03</t>
+          <t>G-16b</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Document verification + qualification</t>
+          <t>Rejecting that bill puts the material back for the next bill</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>verified 5/5; qualification 91/100</t>
+          <t>RA-009 rejected; after reject MI-002 recoveredIn=null</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
@@ -2526,22 +4652,22 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>V04</t>
+          <t>G-15</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Approval Procurement → Legal → Finance (three people) → Active master</t>
+          <t>Equipment register and deployment on a work order</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Active / Spend Authorized; approvers Arjun Mehta, Neha Kulkarni, Rohit Shah</t>
+          <t>VEN-001 register rows 3; WO-001 deployments 3</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
@@ -2553,22 +4679,22 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>V05</t>
+          <t>G-15b</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>RFQ created and sent (new vendor + Konkan)</t>
+          <t>Equipment with expired fitness cannot be deployed</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>RFQ-004 Sent, invited VEN-014, VEN-011</t>
+          <t>"Tipper 10 cum: fitness / insurance expired 25 Sept 2026 — can't deploy"; deployed=false</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
@@ -2580,22 +4706,22 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>V06</t>
+          <t>G-17</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Vendor quotes through the secure link</t>
+          <t>Daily progress report: add, duplicate date blocked</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>quote SST/Q/101 Under review</t>
+          <t>WO-002 reports 1; second report same day blocked=true</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -2607,22 +4733,22 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>V07</t>
+          <t>G-09</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Evaluation + award with recommendation → draft PO</t>
+          <t>Cost by WBS: budget → committed → executed → billed</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>PO-004 Draft for VEN-014, award note "Only compliant quote, L1"</t>
+          <t>WBS rows with budget/committed/executed shown</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
@@ -2634,22 +4760,22 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 4 — quantity &amp; execution</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>V08</t>
+          <t>G-09b</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>PO approval by Procurement Head (not the buyer) → Issued</t>
+          <t>Work order needs a WBS element</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>buyer tried: Draft; Arjun: Issued (approved by Arjun Mehta)</t>
+          <t>save disabled without WBS=true, with WBS=false</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
@@ -2661,22 +4787,22 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>V09</t>
+          <t>G-18a</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Delivery → goods receipt (acceptance)</t>
+          <t>Vendor submits an invoice in the portal → waits for AP review, not payable</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>1 GRN, received 40</t>
+          <t>INV-010 review=Pending; drawer shows AP review=true; payment button hidden</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
@@ -2688,22 +4814,22 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>V10</t>
+          <t>G-18b</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Vendor submits invoice in the portal → AP validation (Accounts) → accepted</t>
+          <t>Duplicate invoice number rejected in the portal</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>INV-010 review Accepted by Anita Joshi; 3-way match against PO-004</t>
+          <t>duplicate blocked</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
@@ -2715,22 +4841,22 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>V11</t>
+          <t>G-18c</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Payment (Finance — not the AP reviewer) → Paid</t>
+          <t>AP review: invoice can't be paid until accepted; accepting makes it payable</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>reviewer blocked: true; status paid by Rohit Shah</t>
+          <t>before review: payment button hidden; after accept: Accepted (by demo); payment button shown</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
@@ -2742,22 +4868,22 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>V12</t>
+          <t>G-18d</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Performance: vendor gets a score after delivery</t>
+          <t>Rejected invoice returns to the vendor; corrected invoice can be resubmitted</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>listed on the scorecard</t>
+          <t>portal row shows Rejected=true; same number allowed again=true</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
@@ -2769,22 +4895,22 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>V13</t>
+          <t>G-10a</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Suspension: hold (All) makes the portal read-only; release restores</t>
+          <t>Retention after DLP needs a handover certificate</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>portal read-only while on hold</t>
+          <t>raise disabled=true; "No handover certificate yet — issue it in Close-out &amp; Handover first"</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
@@ -2796,22 +4922,22 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>V14</t>
+          <t>G-10b</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Closure: vendor made inactive — portal access ends</t>
+          <t>Punch item blocks the final inspection until closed</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Inactive; portal: suspended</t>
+          <t>inspection disabled with open snag=true; after contractor rectified + verified: disabled=false</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
@@ -2823,22 +4949,22 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>C01</t>
+          <t>G-10c</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Contractor registration with statutory documents</t>
+          <t>Failed final inspection → snags to punch list; pass → handover certificate</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>VEN-015 Pending Approval (Labor), 9 documents</t>
+          <t>snags after failed inspection 1; handover 2026-09-30 by demo; status Active</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
@@ -2850,22 +4976,22 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>C02</t>
+          <t>G-10d</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Technical / financial / legal / HSE qualification + insurance + document verification</t>
+          <t>Final bill settles remaining work and stops further billing</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>docs verified 9/9; WC policy Verified; score 79</t>
+          <t>final checkbox preset=true; final bill RA-009 Submitted; WO-004 offered again=false</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
@@ -2877,22 +5003,22 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>C03</t>
+          <t>G-10e</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Approval → contractor master Active</t>
+          <t>Stage tracker on the close-out list</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Active / Spend Authorized</t>
+          <t>CTR-004 row: Final payment</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
@@ -2904,22 +5030,22 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>C04</t>
+          <t>G-11b</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Mobilisation checklist completed</t>
+          <t>Fully settled contract (CTR-005) closes after retention release</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>7/7 done</t>
+          <t>open items before close: none; CTR-005 Closed, WO-006 Closed</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
@@ -2931,22 +5057,22 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Final full-system test</t>
+          <t>Batch 5 — close-out &amp; portal invoices</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>C05</t>
+          <t>G-11c</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>Tender (RFQ) with BOQ → contractor rate submission</t>
+          <t>Closed contract: measurement book frozen</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>RFQ-005: rate 178 submitted</t>
+          <t>WO-006 in measurement picker: false</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
@@ -2963,17 +5089,17 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>C06</t>
+          <t>V01</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Technical + commercial evaluation → award as contract (BOQ carried over)</t>
+          <t>Registration (Tier 1) with documents — submitted</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>CTR-007 Draft, BOQ 3000 nos @ 178</t>
+          <t>VEN-014 Pending Approval, 5 docs pending verification</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
@@ -2990,17 +5116,17 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>C07</t>
+          <t>V02</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Contract approval Legal → Finance, performance BG, signing</t>
+          <t>Final approval blocked until documents verified and qualification done</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Active; approvals Legal Counsel: Neha Kulkarni, Finance Controller: Rohit Shah; signed by Arjun Mehta</t>
+          <t>Open before final approval: PAN Card: awaiting verification · GST Certificate: awaiting verification · Cancell</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
@@ -3017,17 +5143,17 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>C08</t>
+          <t>V03</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Project → WBS → work order from contract BOQ → contractor acceptance</t>
+          <t>Document verification + qualification</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>WO-007 under Skyline Towers — Phase 1 › 1.1 Site enabling; line boqRef S1; acceptance Accepted</t>
+          <t>verified 5/5; qualification 91/100</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
@@ -3044,17 +5170,17 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>C09</t>
+          <t>V04</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>Mobilisation on site: equipment, material issue, daily progress</t>
+          <t>Approval Procurement → Legal → Finance (all three stages) → Active master</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>equipment 1, material issues 1, DPRs 1</t>
+          <t>Active / Spend Authorized; stages Procurement Approved, Legal Approved, Finance Approved</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
@@ -3071,17 +5197,17 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>V05</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Work execution → measurement → contractor agreement → JMS → inspection</t>
+          <t>RFQ created and sent (new vendor + Konkan)</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>MB-034: 1800 cum, JMS Signed (contractor agreed true), inspection Passed</t>
+          <t>RFQ-004 Sent, invited VEN-014, VEN-011</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
@@ -3098,17 +5224,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>V06</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>RA bill (with material recovery) → verification → certification → approval → invoice → payment</t>
+          <t>Vendor quotes through the secure link</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>RA-009: gross 320400, material 46000, retention 16020, net 274400; Submitted:Sneha Iyer → Verified:demo → Certified:Karan Desai → Approved:Vikram Rao → Paid:Anita Joshi; invoice INV-011</t>
+          <t>quote SST/Q/101 Under review</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
@@ -3125,17 +5251,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>V07</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Variation: extra quantity via change order (Project Manager approval)</t>
+          <t>Evaluation + award with recommendation → draft PO</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>WO qty now 3400 (CO +400)</t>
+          <t>PO-004 Draft for VEN-014, award note "Only compliant quote, L1"</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
@@ -3152,17 +5278,17 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>V08</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Balance work measured → WO completed</t>
+          <t>PO approval (Approval Management) → Issued</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>MB-035 1600 cum; WO Completed</t>
+          <t>Issued (approved by demo)</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
@@ -3179,17 +5305,17 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>V09</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Performance rating</t>
+          <t>Delivery → goods receipt (acceptance)</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>1 rating(s)</t>
+          <t>1 GRN, received 40</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
@@ -3206,17 +5332,17 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>V10</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Punch list → final inspection → handover certificate</t>
+          <t>Vendor submits invoice in the portal → AP validation (Accounts) → accepted</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>handover 2026-09-30 by Vikram Rao; status Active (DLP running)</t>
+          <t>INV-010 review Accepted by demo; 3-way match against PO-004</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
@@ -3233,17 +5359,17 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>V11</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Final bill → certification → final payment</t>
+          <t>Payment (after AP acceptance) → Paid</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>RA-010 final=true Paid, gross 284800</t>
+          <t>status paid by demo on 2026-09-30</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
@@ -3260,17 +5386,17 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>V12</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>DLP end → retention release (Finance approval, Accounts release) → BG returned</t>
+          <t>Performance: vendor gets a score after delivery</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>RR-002 ₹30260 Released (approved Rohit Shah, released Anita Joshi); BG Returned</t>
+          <t>listed on the scorecard</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
@@ -3287,17 +5413,17 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>V13</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>Contract closure — checklist complete, WO frozen</t>
+          <t>Suspension: hold (All) makes the portal read-only; release restores</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>open before close: none; contract Closed, WO Closed</t>
+          <t>portal read-only while on hold</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
@@ -3314,20 +5440,533 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
+          <t>V14</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Closure: vendor made inactive — portal access ends</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Inactive; portal: suspended</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Contractor registration with statutory documents</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>VEN-015 Pending Approval (Labor), 9 documents</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Technical / financial / legal / HSE qualification + insurance + document verification</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>docs verified 9/9; WC policy Verified; score 79</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Approval → contractor master Active</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Active / Spend Authorized</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Mobilisation: blocked until the background check is clear, then checklist completed</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>before check: 5/7 (site items blocked); after clear check: 7/7</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Tender (RFQ) with BOQ → contractor rate submission</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>RFQ-005: rate 178 submitted</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Technical + commercial evaluation → award as contract (BOQ carried over)</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>CTR-007 Draft, BOQ 3000 nos @ 178</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Contract approval Legal → Finance, performance BG, signing</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Active; approvals Legal Counsel: demo, Finance Controller: demo; signed by demo</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Project → WBS → work order from contract BOQ → contractor acceptance</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>WO-007 under Skyline Towers — Phase 1 › 1.1 Site enabling; line boqRef S1; acceptance Accepted</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Mobilisation on site: equipment, material issue, daily progress</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>equipment 1, material issues 1, DPRs 1</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Work execution → measurement → contractor agreement → JMS → inspection</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>MB-034: 1800 cum, JMS Signed (contractor agreed true), inspection Passed</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>RA bill (with material recovery) → verification → certification → approval → invoice → payment</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>RA-009: gross 320400, material 46000, retention 16020, net 274400; Submitted:demo → Verified:demo → Certified:demo → Approved:demo → Paid:demo; invoice INV-011</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Variation: extra quantity via change order (Project Manager approval)</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>WO qty now 3400 (CO +400)</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Balance work measured → WO completed</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>MB-035 1600 cum; WO Completed</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Performance rating</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>1 rating(s)</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Punch list → final inspection → handover certificate</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>handover 2026-09-30 by demo; status Active (DLP running)</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Final bill → certification → final payment</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>RA-010 final=true Paid, gross 284800</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>DLP end → retention release (Finance approval, Accounts release) → BG returned</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>RR-002 ₹30260 Released (approved demo, released demo); BG Returned</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Contract closure — checklist complete, WO frozen</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>open before close: none; contract Closed, WO Closed</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>Final full-system test</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>Data continuity — one ID chain from registration to payment</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>vendor VEN-014 → RFQ-004 → PO-004 → INV-010 → paid | contractor VEN-015 → RFQ-005 → CTR-007 → Skyline Towers — Phase 1 › 1.1 Site enabling → BOQ S1 → WO-007 → RA-010, RA-009 → INV-012, INV-011 → paid → Closed</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="E101" s="11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -3398,7 +6037,7 @@
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>Roles</t>
+          <t>Owner (department)</t>
         </is>
       </c>
     </row>
@@ -6063,7 +8702,7 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Owner (department)</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
@@ -6263,7 +8902,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Checklist gate at Finance; SoD; override with reason</t>
+          <t>Checklist gate at Finance; override with reason; Stages come from Procurement Settings → Approval stages</t>
         </is>
       </c>
     </row>
@@ -6337,7 +8976,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>≥ 2 vendors; sourcing gate</t>
+          <t>≥ 2 vendors; sourcing gate; Due date in the future; weights total 100%</t>
         </is>
       </c>
     </row>
@@ -6448,7 +9087,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Approver ≠ awarder; vendor eligible</t>
+          <t>vendor eligible</t>
         </is>
       </c>
     </row>
@@ -6522,7 +9161,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Duplicate no.; billable qty; 3-way match</t>
+          <t>Duplicate no.; billable qty; 3-way match; Duplicate check ignores case and spaces; can't bill more than received</t>
         </is>
       </c>
     </row>
@@ -6559,7 +9198,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Holds, compliance, bank; SoD</t>
+          <t>Holds, compliance, bank; Payment date not in the future or before the bill date</t>
         </is>
       </c>
     </row>
@@ -6755,7 +9394,7 @@
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Owner (department)</t>
         </is>
       </c>
       <c r="E1" s="5" t="inlineStr">
@@ -6881,7 +9520,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Checklist gate; SoD</t>
+          <t>Checklist gate; Qualification status: Qualified / with exceptions / Not qualified / Expired</t>
         </is>
       </c>
     </row>
@@ -6918,7 +9557,7 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Gates the first WO</t>
+          <t>Gates the first WO; Background check clear (litigation and watchlist) within 12 months</t>
         </is>
       </c>
     </row>
@@ -7029,7 +9668,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>PBG before signing; SoD</t>
+          <t>PBG before signing</t>
         </is>
       </c>
     </row>
@@ -7066,7 +9705,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>WBS required; lines from contract BOQ; issue gates</t>
+          <t>WBS required; lines from contract BOQ; issue gates; Warning above the contractor's qualification value limit</t>
         </is>
       </c>
     </row>
@@ -7177,7 +9816,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Quantity cap; open NCR blocks; material auto; SoD</t>
+          <t>Quantity cap; open NCR blocks; material auto</t>
         </is>
       </c>
     </row>
@@ -7214,7 +9853,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Raiser ≠ approver</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7436,7 +10075,7 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Handover, DLP, retention BG</t>
+          <t>Handover, DLP, retention BG; Release ≤ available; BG-backed release needs the guarantee reference</t>
         </is>
       </c>
     </row>
@@ -7562,7 +10201,7 @@
       </c>
       <c r="E1" s="5" t="inlineStr">
         <is>
-          <t>Who</t>
+          <t>Usually done by</t>
         </is>
       </c>
       <c r="F1" s="5" t="inlineStr">
@@ -7631,7 +10270,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>SoD</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7885,7 +10524,11 @@
           <t>Procurement Head</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7979,7 +10622,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>≠ creator / awarder</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8009,7 +10652,11 @@
           <t>Stores</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8071,7 +10718,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>Gate + SoD</t>
+          <t>Gate +</t>
         </is>
       </c>
     </row>
@@ -8135,7 +10782,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>SoD</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8357,7 +11004,11 @@
           <t>Contractor</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -8481,7 +11132,11 @@
           <t>system</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -8509,7 +11164,11 @@
           <t>Contractor</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -8571,7 +11230,7 @@
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>≠ recorder</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8601,7 +11260,11 @@
           <t>Contractor / site</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -8629,7 +11292,11 @@
           <t>Inspector</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -8659,7 +11326,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>SoD</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8721,7 +11388,11 @@
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -8781,7 +11452,11 @@
           <t>Accounts / Finance</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -8811,7 +11486,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>≠ requester</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8843,7 +11518,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>≠ requester / approver</t>
+          <t>/ approver</t>
         </is>
       </c>
     </row>
@@ -8875,7 +11550,7 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>≠ raiser; lines raise WO qty</t>
+          <t>lines raise WO qty</t>
         </is>
       </c>
     </row>
@@ -8905,7 +11580,11 @@
           <t>Contractor</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -8933,7 +11612,11 @@
           <t>PM / Site Eng</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -8961,7 +11644,11 @@
           <t>Procurement / Finance (encash)</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9706,17 +12393,17 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -11214,17 +13901,17 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -11266,17 +13953,17 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -11318,17 +14005,17 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -11370,17 +14057,17 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -11871,7 +14558,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Personas with roles ('Acting as' switcher on every page); each step requires its role; the same person can't act twice on a record or approve their own submission; payment by Accounts / Finance only and not by the bill's enterer / approver</t>
+          <t>Withdrawn at the user's request: the 'Acting as' switcher, per-step role checks and one-person-per-step rules were removed. Every step is still recorded with who did it and when; stage order and all business gates remain.</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -11886,7 +14573,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -12654,7 +15341,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Replaced by the persona shown in 'Acting as'</t>
+          <t>Withdrawn with the role model: there is no 'Your role' setting and no persona switcher.</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -12669,7 +15356,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -12681,7 +15368,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>SoD check in the payment run</t>
+          <t>Withdrawn with the role model: the payment run keeps its gates (review, holds, compliance, bank verification) but no longer checks who entered or approved the bill.</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -12696,7 +15383,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -12708,7 +15395,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Site Engineer role</t>
+          <t>Withdrawn with the role model: any user can sign a JMS; the contractor-agreement or paper-JMS rule stays.</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -12723,7 +15410,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -12735,7 +15422,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Procurement Head, not the requester</t>
+          <t>Withdrawn with the role model: rate approval is a separate step but has no role check.</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -12750,7 +15437,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Passed</t>
+          <t>Withdrawn</t>
         </is>
       </c>
     </row>
@@ -12822,1405 +15509,910 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Suite</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Test ID</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>Scenario</t>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>How it works now</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Test IDs</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-01</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>G-27</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Submit registration with no documents</t>
+          <t>Labour rates: rate ≥ minimum wage, OT multiplier 1–3, a revision starts after the current version, duplicate card blocked</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Rate card form checks each rule inline and disables Save</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-02</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>G-27b</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Save as draft still allowed without documents; submit from drawer blocked</t>
+          <t>Advance to contractor ≤ contract value and ≤ mobilisation-advance %; date not in the future; reference required</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Advance form on Retention &amp; Deductions checks the caps, date and reference</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Built — no automated test</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-03</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>G-13a</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Wrong role cannot decide a vendor stage</t>
+          <t>Retention release ≤ available; a BG-backed release needs the guarantee reference</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Release request capped at the balance; picking 'against retention BG' requires a guarantee from the BG register</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>G-25b, C17</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-04</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>G-13b</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Legal Counsel approves; the same person cannot approve Finance</t>
+          <t>Add worker: DOB required and age ≥ 18, mobile checked, unique gate pass, duplicate-name warning</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Add worker form (attendance) validates each field; duplicate name warns</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-05</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>Bills &amp; payments</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Final approval blocked by open checklist (no WC insurance)</t>
+          <t>Duplicate invoice numbers blocked, ignoring case and spaces</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Bill number normalised before the duplicate check</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>B-01, G-19</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-06</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>G-01b</t>
+          <t>Bills &amp; payments</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Finance Controller approves with override + reason (logged)</t>
+          <t>Can't bill more than received; warning when the rate is above the PO rate</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Line quantity capped at received (or ordered) minus billed; rate above PO shows a warning</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>G-16, V10</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-07</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>G-02</t>
+          <t>Bills &amp; payments</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Registration tier cannot be switched directly; request → Finance approval</t>
+          <t>Due date shown and overridable</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Due date defaults from payment terms; override needs a reason</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Built — no automated test</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-08</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>G-28</t>
+          <t>Bills &amp; payments</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Hold past its release date ends automatically</t>
+          <t>Payment date not in the future and not before the bill date</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Payment dialog blocks both</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-09</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>G-19</t>
+          <t>Bills &amp; payments</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Duplicate vendor bill number blocked</t>
+          <t>Debit note ≤ outstanding; instalments after the bill date, in order, totalling 100%; advance adjustment ≤ what's left</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Invoice drawer forms check each rule</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Built — no automated test</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-10</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>G-14</t>
+          <t>Bills &amp; payments</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Non-compliant vendor stopped at PO</t>
+          <t>Select payable</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Vendor Bills: select every payable bill in one click for a payment run</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-11</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>G-05</t>
+          <t>Bills &amp; payments</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>On-hold (All) contractor: portal read-only</t>
+          <t>Accruals</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Vendor Bills → Accruals: goods received but not yet billed, by PO and vendor</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-12</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>G-26</t>
+          <t>Purchasing</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Inactive vendor loses an open portal session</t>
+          <t>RFQs: due date in the future, weights total 100%, line checks, ≥ 2 vendors</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>New RFQ lists every open problem in the footer and disables Save</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>P-01, V05</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Batch 1 — vendor gates, roles, SoD</t>
+          <t>MG-13</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>G-13c</t>
+          <t>Purchasing</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Payment needs Accounts/Finance role</t>
+          <t>Quotations: discount, lead time and validity checks</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Quote form: discount 0–100%, lead time ≥ 0 days, validity after the quote date</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Built — no automated test</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-14</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>G-25a</t>
+          <t>Purchasing</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Retention release: requester and wrong role cannot approve</t>
+          <t>PO and GRN: delivery date, tolerance 0–20%, inspection result consistent with quantities, reason for rejected goods</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>New PO and GRN forms check each rule</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>V09</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-15</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>G-25b</t>
+          <t>Purchasing</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Finance approves, approver cannot release, Accounts releases</t>
+          <t>Blanket orders: dates, lines, no duplicate item</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Blanket order form checks dates, lines and duplicate items</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Built — no automated test</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-16</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>G-13d</t>
+          <t>Purchasing</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>RA bill: each certification step needs its role and a different person</t>
+          <t>Exchange rate: editable on the quote with the rupee equivalent shown</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Quote form has a currency and FX-rate field; INR equivalent shown beside the total</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Built — no automated test</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-17</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>G-03a</t>
+          <t>Approvals</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Contract for an unapproved contractor cannot be submitted</t>
+          <t>Configurable approval stages</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Procurement Settings → Vendor / Contract approval stages: add, rename, reorder, remove; vendor stages can apply to contractors or non-contractors only; contract stages can start at a minimum value. Records already in approval keep their stages</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>S-01, S-02</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-18</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>G-03b</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>New contract: draft → Legal → Finance → sign (needs performance BG)</t>
+          <t>Version history, who verified and when, the 5 MB / file-type limit on every upload dialog, withdraw or delete</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Each upload keeps earlier versions; verification stamps name and time; uploads over 5 MB or of other types are refused; withdraw (pending) or delete (with reason)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>M-03, V03</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-19</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>G-22</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>BG register: extend and return</t>
+          <t>Qualification status (Qualified, Qualified with exceptions, Not qualified, Expired) with project value limits; warning when a WO goes over the limit</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Qualification tab sets the value limit and exceptions; results table shows status and limit; WO and contract forms warn above the limit; not-qualified contractors can't get work orders</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Q-01, Q-02</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-20</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Blocked contractor: contract hidden from WO picker; draft WO cannot be issued</t>
+          <t>Mobilisation blocked until the background check is clear</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Background check form (litigation, watchlist, date, finding); work-order issue and site checklist items blocked until clear and &lt; 12 months old</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Q-03, Q-04, C04</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-21</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>G-24</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>First work order waits for the mobilisation checklist</t>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Policy number format and duplicate, insurer, cover &gt; 0, valid till after valid from and not already expired</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>F-02, C02</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-22</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>G-21</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Suspend and resume a work order</t>
+          <t>Placing a hold</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Reason ≥ 5 characters; release date in the future and within a year (blank = indefinite); same rules on bulk hold</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>F-01, V13</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-23</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>G-07</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Change order with a quantity line raises the WO quantity on approval</t>
+          <t>Corrective action plans</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Issue, actions, owner required; due date in the future and within 180 days</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Built — no automated test</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-24</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>G-11</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Contract closure checklist blocks closing an active contract</t>
+          <t>Performance ratings</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Every rating 1–5; incidents a whole number; remarks required when a rating is 2 or below or incidents are reported; one rating per period and WO</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>F-03, C14</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Batches 2–3 — approvals, award, contract lifecycle</t>
+          <t>MG-25</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>G-08/G-20</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Contractor RFQ award → draft contract with BOQ; recommendation required</t>
+          <t>RA bills</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Period dates in order, deductions not negative, net not below zero, note required</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>C11, C16</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>MG-26</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>G-23</t>
+          <t>Vendor master</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Contractor agrees a measurement in the portal; engineer countersigns without a paper sheet</t>
+          <t>Bank verification, foreign vendors, field formats</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>New accounts start Unverified; verify / reject with reason; holder name checked; foreign vendors use tax ID + SWIFT; PIN, website, IFSC, account formats</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>M-01, M-02, V01</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Batch 4 — quantity &amp; execution</t>
+          <t>MG-27</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>G-12a</t>
+          <t>Roles</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Signed but uninspected measurement is not billable</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>G-12b</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Inspection fails → NCR → QS certification of WO-001 blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>G-12c</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Rework → re-inspection pass closes the NCR and makes the entry billable</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>G-06</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Quantity above the WO blocks the RA bill until a change order raises it</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>G-16</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Unrecovered free-issue material is deducted automatically and linked to the bill</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>G-16b</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Rejecting that bill puts the material back for the next bill</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>G-15</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Equipment register and deployment on a work order</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>G-15b</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Equipment with expired fitness cannot be deployed</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>G-17</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Daily progress report: add, duplicate date blocked</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>G-09</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Cost by WBS: budget → committed → executed → billed</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Batch 4 — quantity &amp; execution</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>G-09b</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Work order needs a WBS element</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>G-18a</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Vendor submits an invoice in the portal → waits for AP review, not payable</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>G-18b</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Duplicate invoice number rejected in the portal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>G-18c</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>AP review: Procurement cannot accept; Accounts accepts → payable</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>G-18d</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Rejected invoice returns to the vendor; corrected invoice can be resubmitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>G-10a</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Retention after DLP needs a handover certificate</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>G-10b</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Punch item blocks the final inspection until closed</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>G-10c</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>Failed final inspection → snags to punch list; pass → handover certificate</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>G-10d</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Final bill settles remaining work and stops further billing</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>G-10e</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Stage tracker on the close-out list</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>G-11b</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Fully settled contract (CTR-005) closes after retention release</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Batch 5 — close-out &amp; portal invoices</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>G-11c</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Closed contract: measurement book frozen</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>V01</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Registration (Tier 1) with documents — submitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>V02</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>Final approval blocked until documents verified and qualification done</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>V03</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Document verification + qualification</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>V04</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>Approval Procurement → Legal → Finance (three people) → Active master</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>V05</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>RFQ created and sent (new vendor + Konkan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>V06</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Vendor quotes through the secure link</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>V07</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Evaluation + award with recommendation → draft PO</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>V08</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>PO approval by Procurement Head (not the buyer) → Issued</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>V09</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Delivery → goods receipt (acceptance)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>V10</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>Vendor submits invoice in the portal → AP validation (Accounts) → accepted</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>V11</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Payment (Finance — not the AP reviewer) → Paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>V12</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Performance: vendor gets a score after delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>V13</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Suspension: hold (All) makes the portal read-only; release restores</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>V14</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Closure: vendor made inactive — portal access ends</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>C01</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Contractor registration with statutory documents</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>C02</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Technical / financial / legal / HSE qualification + insurance + document verification</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>C03</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>Approval → contractor master Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>C04</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Mobilisation checklist completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>C05</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Tender (RFQ) with BOQ → contractor rate submission</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>C06</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Technical + commercial evaluation → award as contract (BOQ carried over)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>C07</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>Contract approval Legal → Finance, performance BG, signing</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>C08</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Project → WBS → work order from contract BOQ → contractor acceptance</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>C09</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Mobilisation on site: equipment, material issue, daily progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>Work execution → measurement → contractor agreement → JMS → inspection</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>RA bill (with material recovery) → verification → certification → approval → invoice → payment</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Variation: extra quantity via change order (Project Manager approval)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Balance work measured → WO completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>C14</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>Performance rating</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>C15</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>Punch list → final inspection → handover certificate</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>C16</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Final bill → certification → final payment</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>DLP end → retention release (Finance approval, Accounts release) → BG returned</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
-        <is>
-          <t>C18</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>Contract closure — checklist complete, WO frozen</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Final full-system test</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Data continuity — one ID chain from registration to payment</t>
+          <t>Remove the 'Acting as' switcher, role checks and one-person-per-step</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Removed everywhere; approvals still run stage by stage and every action is logged with the signed-in user</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>R-01, G-13a, G-13b</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
